--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\we-compare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B4BD3-B3FD-4ABD-B533-30EFD2D54D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D69F0D9-4A1E-476C-A210-FD10D7F9EE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -347,30 +356,42 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <v>32</v>
+      </c>
+      <c r="F2">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -378,12 +399,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E11">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>32</v>
       </c>
